--- a/sample_data/descriptions.xlsx
+++ b/sample_data/descriptions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,6 +449,11 @@
           <t>Steward</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -471,6 +476,11 @@
           <t>Finance</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -489,6 +499,11 @@
           <t>Finance</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -503,6 +518,11 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -521,6 +541,11 @@
           <t>Data Governance</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -535,6 +560,11 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -557,6 +587,11 @@
           <t>Finance</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -579,6 +614,11 @@
           <t>Data Governance</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -597,6 +637,11 @@
           <t>People Analytics</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -615,6 +660,11 @@
           <t>People Analytics</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -637,6 +687,11 @@
           <t>Data Governance</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -659,6 +714,11 @@
           <t>People Analytics</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -681,6 +741,11 @@
           <t>Data Governance</t>
         </is>
       </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -699,6 +764,11 @@
           <t>People Analytics</t>
         </is>
       </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -717,6 +787,11 @@
           <t>People Analytics</t>
         </is>
       </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -735,6 +810,11 @@
           <t>Finance</t>
         </is>
       </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -757,6 +837,11 @@
           <t>Finance</t>
         </is>
       </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -779,6 +864,11 @@
           <t>Data Governance</t>
         </is>
       </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -797,6 +887,11 @@
           <t>Marketing Analytics</t>
         </is>
       </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -815,6 +910,11 @@
           <t>People Analytics</t>
         </is>
       </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -833,6 +933,11 @@
           <t>People Analytics</t>
         </is>
       </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -851,6 +956,11 @@
           <t>Sales Ops</t>
         </is>
       </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -873,6 +983,11 @@
           <t>Sales Ops</t>
         </is>
       </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -891,6 +1006,11 @@
           <t>Sales Ops</t>
         </is>
       </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -909,6 +1029,11 @@
           <t>Finance</t>
         </is>
       </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -927,6 +1052,11 @@
           <t>Finance</t>
         </is>
       </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -945,6 +1075,11 @@
           <t>People Analytics</t>
         </is>
       </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -959,6 +1094,11 @@
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -981,6 +1121,11 @@
           <t>Data Governance</t>
         </is>
       </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1003,6 +1148,11 @@
           <t>Sales Ops</t>
         </is>
       </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1021,6 +1171,11 @@
           <t>Sales Ops</t>
         </is>
       </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1035,6 +1190,11 @@
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1053,6 +1213,11 @@
           <t>Marketing Analytics</t>
         </is>
       </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1075,6 +1240,11 @@
           <t>People Analytics</t>
         </is>
       </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1093,6 +1263,11 @@
           <t>Data Governance</t>
         </is>
       </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1111,6 +1286,11 @@
           <t>Sales Ops</t>
         </is>
       </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1133,6 +1313,11 @@
           <t>Finance</t>
         </is>
       </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1155,6 +1340,11 @@
           <t>Sales Ops</t>
         </is>
       </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1173,6 +1363,11 @@
           <t>Sales Ops</t>
         </is>
       </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1191,6 +1386,11 @@
           <t>Finance</t>
         </is>
       </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1207,6 +1407,11 @@
       <c r="D41" t="inlineStr">
         <is>
           <t>Finance</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
